--- a/data/FiskLab_stable-isotopes_biomass_data/Biomass_StableIsotopes data_CHeuvel_edited.xlsx
+++ b/data/FiskLab_stable-isotopes_biomass_data/Biomass_StableIsotopes data_CHeuvel_edited.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trentu-my.sharepoint.com/personal/sandraklemet_trentu_ca/Documents/Documents/Etudes/Trent/Xenopoulos lab/Projects/LakeErie_animal-excretion/data/FiskLab_stable-isotopes_biomass_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{55752C12-F562-4B7D-A1A1-FB99C56ACF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52A54908-22E1-456E-8E2F-E8C15605920E}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="8_{55752C12-F562-4B7D-A1A1-FB99C56ACF18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{858F1BE5-E0CC-48E2-858A-49DFF062F1A9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{062B1D82-E5B8-4B6C-AB2C-D46774B067F9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{062B1D82-E5B8-4B6C-AB2C-D46774B067F9}"/>
   </bookViews>
   <sheets>
     <sheet name="Biomass Data" sheetId="1" r:id="rId1"/>
@@ -40,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="806" uniqueCount="172">
-  <si>
-    <t>Biomass Kg/ha</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="177">
   <si>
     <t>Species</t>
   </si>
@@ -556,19 +553,43 @@
   </si>
   <si>
     <t>Mean_d15N</t>
+  </si>
+  <si>
+    <t>Biomass Kg/ha in Western Basin</t>
+  </si>
+  <si>
+    <t>Gizzard shad</t>
+  </si>
+  <si>
+    <t>Log perch</t>
+  </si>
+  <si>
+    <t>Yellow perch</t>
+  </si>
+  <si>
+    <t>W.B Yellow Perch</t>
+  </si>
+  <si>
+    <t>Lake wide Biomass Data (Kg/ha)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -597,18 +618,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -923,25 +954,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60AB9DB4-04CE-40F2-8C4C-AF4C8D6FA91D}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.54296875" customWidth="1"/>
+    <col min="4" max="4" width="10.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="1">
         <v>2016</v>
@@ -964,7 +996,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3">
         <v>0.51570487447840629</v>
@@ -987,7 +1019,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4">
         <v>1.4843694523261911E-2</v>
@@ -1010,7 +1042,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5">
         <v>0.100803244324578</v>
@@ -1033,7 +1065,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6">
         <v>12.975733420592341</v>
@@ -1056,7 +1088,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>1.8622407326302008</v>
@@ -1075,6 +1107,29 @@
       </c>
       <c r="G7">
         <v>5.0365728528818288</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="5">
+        <v>46.048534119999999</v>
+      </c>
+      <c r="C8" s="5">
+        <v>46.732286799999997</v>
+      </c>
+      <c r="D8" s="5">
+        <v>35.544879999999999</v>
+      </c>
+      <c r="E8" s="5">
+        <v>29.33484</v>
+      </c>
+      <c r="F8" s="5">
+        <v>91.386446129999996</v>
+      </c>
+      <c r="G8">
+        <v>52.646818469999999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
@@ -1114,7 +1169,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13">
         <v>7.3088669992163499E-2</v>
@@ -1152,12 +1207,161 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H14" t="s">
-        <v>166</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.35">
+      <c r="A16" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="A17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2016</v>
+      </c>
+      <c r="C17" s="5">
+        <v>2017</v>
+      </c>
+      <c r="D17" s="5">
+        <v>2018</v>
+      </c>
+      <c r="E17" s="5">
+        <v>2019</v>
+      </c>
+      <c r="F17" s="5">
+        <v>2020</v>
+      </c>
+      <c r="G17" s="5">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.29481154500000001</v>
+      </c>
+      <c r="C18" s="5">
+        <v>1.8343823299999999</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.299537</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0.24527299999999999</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1.5348229200000001</v>
+      </c>
+      <c r="G18">
+        <v>0.69021067999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="A19" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B19" s="5">
+        <v>6.9886700000000004E-4</v>
+      </c>
+      <c r="C19" s="5">
+        <v>6.3414999999999999E-4</v>
+      </c>
+      <c r="D19" s="6">
+        <v>4.0599999999999998E-5</v>
+      </c>
+      <c r="E19" s="5">
+        <v>3.4200000000000002E-4</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1.4584E-4</v>
+      </c>
+      <c r="G19">
+        <v>6.6331599999999995E-4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="A20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0.15317381499999999</v>
+      </c>
+      <c r="C20" s="5">
+        <v>0.17322140999999999</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.124649</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0.23880899999999999</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.114981425</v>
+      </c>
+      <c r="G20">
+        <v>0.16141213200000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="A21" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5">
+        <v>2.9962447559999998</v>
+      </c>
+      <c r="C21" s="5">
+        <v>4.0498032899999998</v>
+      </c>
+      <c r="D21" s="5">
+        <v>3.928868</v>
+      </c>
+      <c r="E21" s="5">
+        <v>2.4504079999999999</v>
+      </c>
+      <c r="F21" s="5">
+        <v>3.9996879010000002</v>
+      </c>
+      <c r="G21">
+        <v>4.1384511689999997</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="A22" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B22" s="5">
+        <v>6.382081157</v>
+      </c>
+      <c r="C22" s="5">
+        <v>5.3030500800000002</v>
+      </c>
+      <c r="D22" s="5">
+        <v>2.5902370000000001</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1.112557</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1.8527943440000001</v>
+      </c>
+      <c r="G22">
+        <v>10.3817766</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B1:G1"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1169,106 +1373,103 @@
   <dimension ref="A1:Y87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="8.7265625" style="5"/>
-    <col min="10" max="10" width="35.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="8.7265625" style="5"/>
-    <col min="13" max="13" width="14.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" t="s">
         <v>20</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" t="s">
         <v>21</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="R1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="S1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="T1" t="s">
         <v>26</v>
       </c>
-      <c r="T1" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" t="s">
+        <v>167</v>
+      </c>
+      <c r="V1" t="s">
         <v>168</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="W1" t="s">
         <v>169</v>
       </c>
-      <c r="W1" s="5" t="s">
+      <c r="X1" t="s">
+        <v>166</v>
+      </c>
+      <c r="Y1" t="s">
         <v>170</v>
       </c>
-      <c r="X1" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>867</v>
       </c>
       <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>29</v>
       </c>
-      <c r="D2" t="s">
-        <v>30</v>
-      </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>393</v>
@@ -1280,16 +1481,16 @@
         <v>830</v>
       </c>
       <c r="J2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M2" s="2">
         <v>43661</v>
       </c>
       <c r="N2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O2">
         <v>-26.607805410000001</v>
@@ -1307,24 +1508,24 @@
         <v>5.5660993420000002</v>
       </c>
       <c r="T2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>515</v>
       </c>
       <c r="B3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F3">
         <v>61</v>
@@ -1336,16 +1537,16 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="J3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M3" s="2">
         <v>43661</v>
       </c>
       <c r="N3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O3">
         <v>-25.787261749999999</v>
@@ -1363,24 +1564,24 @@
         <v>3.6858143540000001</v>
       </c>
       <c r="T3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>516</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F4">
         <v>48</v>
@@ -1392,16 +1593,16 @@
         <v>1.2</v>
       </c>
       <c r="J4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M4" s="2">
         <v>43661</v>
       </c>
       <c r="N4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O4">
         <v>-24.910736</v>
@@ -1419,24 +1620,24 @@
         <v>3.1398682290000002</v>
       </c>
       <c r="T4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>517</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F5">
         <v>59</v>
@@ -1448,16 +1649,16 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="J5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M5" s="2">
         <v>43661</v>
       </c>
       <c r="N5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O5">
         <v>-24.86522789</v>
@@ -1475,24 +1676,24 @@
         <v>3.4400902960000002</v>
       </c>
       <c r="T5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>518</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6">
         <v>54</v>
@@ -1504,16 +1705,16 @@
         <v>1.7</v>
       </c>
       <c r="J6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M6" s="2">
         <v>43661</v>
       </c>
       <c r="N6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="O6">
         <v>-23.718621410000001</v>
@@ -1531,24 +1732,24 @@
         <v>3.4007363540000002</v>
       </c>
       <c r="T6" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>519</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F7">
         <v>55</v>
@@ -1560,16 +1761,16 @@
         <v>2</v>
       </c>
       <c r="J7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M7" s="2">
         <v>43661</v>
       </c>
       <c r="N7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O7">
         <v>-26.258171749999999</v>
@@ -1587,212 +1788,212 @@
         <v>3.322701066</v>
       </c>
       <c r="T7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="5">
+      <c r="A8">
         <v>435</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8">
         <v>107</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8">
+        <v>11.6</v>
+      </c>
+      <c r="J8" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="5">
-        <v>11.6</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="L8" t="s">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2">
+        <v>43705</v>
+      </c>
+      <c r="N8" t="s">
         <v>54</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M8" s="6">
-        <v>43705</v>
-      </c>
-      <c r="N8" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" s="5">
+      <c r="O8">
         <v>-23.480379859999999</v>
       </c>
-      <c r="P8" s="5">
+      <c r="P8">
         <v>44.942498649999997</v>
       </c>
-      <c r="Q8" s="5">
+      <c r="Q8">
         <v>11.50440961</v>
       </c>
-      <c r="R8" s="5">
+      <c r="R8">
         <v>14.150903189999999</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S8">
         <v>3.175945595</v>
       </c>
-      <c r="T8" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="U8" s="5">
+      <c r="T8" t="s">
+        <v>44</v>
+      </c>
+      <c r="U8">
         <f>AVERAGE(P8:P22)</f>
         <v>51.794115875333326</v>
       </c>
-      <c r="V8" s="5">
+      <c r="V8">
         <f>AVERAGE(R8:R22)</f>
         <v>11.136419494933332</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8">
         <f>AVERAGE(S8:S22)</f>
         <v>5.0821599532666664</v>
       </c>
-      <c r="X8" s="5">
+      <c r="X8">
         <f>AVERAGE(O8:O22)</f>
         <v>-24.145373220666663</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="Y8">
         <f>AVERAGE(Q8:Q22)</f>
         <v>11.343827143333334</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A9" s="5">
+      <c r="A9">
         <v>436</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="5">
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9">
         <v>130</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9">
         <v>118</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <v>21.6</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M9" s="2">
+        <v>43705</v>
+      </c>
+      <c r="N9" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M9" s="6">
+      <c r="O9">
+        <v>-24.30874549</v>
+      </c>
+      <c r="P9">
+        <v>43.323799899999997</v>
+      </c>
+      <c r="Q9">
+        <v>10.85945626</v>
+      </c>
+      <c r="R9">
+        <v>12.7768157</v>
+      </c>
+      <c r="S9">
+        <v>3.390813557</v>
+      </c>
+      <c r="T9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>136</v>
+      </c>
+      <c r="G10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H10">
+        <v>238.8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L10" t="s">
+        <v>33</v>
+      </c>
+      <c r="M10" s="2">
         <v>43705</v>
       </c>
-      <c r="N9" s="5" t="s">
+      <c r="N10" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="5">
-        <v>-24.30874549</v>
-      </c>
-      <c r="P9" s="5">
-        <v>43.323799899999997</v>
-      </c>
-      <c r="Q9" s="5">
-        <v>10.85945626</v>
-      </c>
-      <c r="R9" s="5">
-        <v>12.7768157</v>
-      </c>
-      <c r="S9" s="5">
-        <v>3.390813557</v>
-      </c>
-      <c r="T9" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" s="5">
-        <v>437</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="5">
-        <v>136</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H10" s="5">
-        <v>238.8</v>
-      </c>
-      <c r="J10" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M10" s="6">
-        <v>43705</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="O10" s="5">
+      <c r="O10">
         <v>-23.583802439999999</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10">
         <v>44.376729159999996</v>
       </c>
-      <c r="Q10" s="5">
+      <c r="Q10">
         <v>12.325439190000001</v>
       </c>
-      <c r="R10" s="5">
+      <c r="R10">
         <v>14.06385596</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S10">
         <v>3.1553742640000002</v>
       </c>
-      <c r="T10" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+      <c r="T10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>420</v>
       </c>
       <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
         <v>28</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c r="D11" t="s">
-        <v>30</v>
-      </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F11">
         <v>469</v>
@@ -1804,19 +2005,19 @@
         <v>1281</v>
       </c>
       <c r="J11" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" t="s">
         <v>50</v>
       </c>
-      <c r="K11" t="s">
-        <v>51</v>
-      </c>
       <c r="L11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M11" s="2">
         <v>43724</v>
       </c>
       <c r="N11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O11">
         <v>-24.044771659999999</v>
@@ -1834,24 +2035,24 @@
         <v>7.7182392740000001</v>
       </c>
       <c r="T11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>759</v>
       </c>
       <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
         <v>28</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>29</v>
       </c>
-      <c r="D12" t="s">
-        <v>30</v>
-      </c>
       <c r="E12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F12">
         <v>151</v>
@@ -1863,19 +2064,19 @@
         <v>29</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M12" s="2">
         <v>43725</v>
       </c>
       <c r="N12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O12">
         <v>-21.230762850000001</v>
@@ -1893,24 +2094,24 @@
         <v>3.6606123099999999</v>
       </c>
       <c r="T12" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>760</v>
       </c>
       <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>29</v>
       </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
       <c r="E13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F13">
         <v>165</v>
@@ -1922,19 +2123,19 @@
         <v>43</v>
       </c>
       <c r="J13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M13" s="2">
         <v>43725</v>
       </c>
       <c r="N13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O13">
         <v>-22.85266605</v>
@@ -1952,24 +2153,24 @@
         <v>3.382634135</v>
       </c>
       <c r="T13" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>761</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>29</v>
       </c>
-      <c r="D14" t="s">
-        <v>30</v>
-      </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F14">
         <v>152</v>
@@ -1981,19 +2182,19 @@
         <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M14" s="2">
         <v>43725</v>
       </c>
       <c r="N14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="O14">
         <v>-22.925125619999999</v>
@@ -2011,24 +2212,24 @@
         <v>3.7572618950000001</v>
       </c>
       <c r="T14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>802</v>
       </c>
       <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
         <v>28</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>29</v>
       </c>
-      <c r="D15" t="s">
-        <v>30</v>
-      </c>
       <c r="E15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F15">
         <v>158</v>
@@ -2040,19 +2241,19 @@
         <v>40</v>
       </c>
       <c r="J15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M15" s="2">
         <v>43725</v>
       </c>
       <c r="N15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O15">
         <v>-23.158062560000001</v>
@@ -2070,24 +2271,24 @@
         <v>3.9667750439999998</v>
       </c>
       <c r="T15" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>803</v>
       </c>
       <c r="B16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" t="s">
         <v>28</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>29</v>
       </c>
-      <c r="D16" t="s">
-        <v>30</v>
-      </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F16">
         <v>115</v>
@@ -2099,19 +2300,19 @@
         <v>17</v>
       </c>
       <c r="J16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M16" s="2">
         <v>43725</v>
       </c>
       <c r="N16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O16">
         <v>-23.411309580000001</v>
@@ -2129,48 +2330,48 @@
         <v>3.7605194150000001</v>
       </c>
       <c r="T16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>804</v>
       </c>
       <c r="B17" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" t="s">
         <v>28</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F17">
         <v>116</v>
       </c>
       <c r="G17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H17">
         <v>23</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L17" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M17" s="2">
         <v>43725</v>
       </c>
       <c r="N17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O17">
         <v>-23.35148745</v>
@@ -2188,7 +2389,7 @@
         <v>4.1652938649999998</v>
       </c>
       <c r="T17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -2196,16 +2397,16 @@
         <v>316</v>
       </c>
       <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
         <v>28</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>29</v>
       </c>
-      <c r="D18" t="s">
-        <v>30</v>
-      </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F18">
         <v>410</v>
@@ -2217,20 +2418,20 @@
         <v>900</v>
       </c>
       <c r="I18" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" t="s">
         <v>32</v>
-      </c>
-      <c r="J18" t="s">
-        <v>33</v>
       </c>
       <c r="K18"/>
       <c r="L18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M18" s="2">
         <v>43726</v>
       </c>
       <c r="N18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O18">
         <v>-27.052943930000001</v>
@@ -2248,7 +2449,7 @@
         <v>7.6560899449999997</v>
       </c>
       <c r="T18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -2256,16 +2457,16 @@
         <v>317</v>
       </c>
       <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
         <v>28</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>29</v>
       </c>
-      <c r="D19" t="s">
-        <v>30</v>
-      </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19">
         <v>431</v>
@@ -2278,17 +2479,17 @@
       </c>
       <c r="I19"/>
       <c r="J19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K19"/>
       <c r="L19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M19" s="2">
         <v>43726</v>
       </c>
       <c r="N19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O19">
         <v>-23.188602540000002</v>
@@ -2306,7 +2507,7 @@
         <v>4.8413305959999997</v>
       </c>
       <c r="T19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -2314,16 +2515,16 @@
         <v>318</v>
       </c>
       <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
         <v>28</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>29</v>
       </c>
-      <c r="D20" t="s">
-        <v>30</v>
-      </c>
       <c r="E20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F20">
         <v>340</v>
@@ -2335,20 +2536,20 @@
         <v>501</v>
       </c>
       <c r="I20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K20"/>
       <c r="L20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M20" s="2">
         <v>43726</v>
       </c>
       <c r="N20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O20">
         <v>-25.561288489999999</v>
@@ -2366,7 +2567,7 @@
         <v>6.4562010279999997</v>
       </c>
       <c r="T20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -2374,16 +2575,16 @@
         <v>342</v>
       </c>
       <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
         <v>28</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>29</v>
       </c>
-      <c r="D21" t="s">
-        <v>30</v>
-      </c>
       <c r="E21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F21">
         <v>444</v>
@@ -2395,14 +2596,14 @@
         <v>1140.5999999999999</v>
       </c>
       <c r="I21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" t="s">
         <v>32</v>
-      </c>
-      <c r="J21" t="s">
-        <v>33</v>
       </c>
       <c r="K21"/>
       <c r="L21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M21" s="2">
         <v>43726</v>
@@ -2426,7 +2627,7 @@
         <v>7.4589504609999997</v>
       </c>
       <c r="T21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -2434,16 +2635,16 @@
         <v>784</v>
       </c>
       <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
         <v>28</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>29</v>
       </c>
-      <c r="D22" t="s">
-        <v>30</v>
-      </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F22">
         <v>440</v>
@@ -2456,19 +2657,19 @@
       </c>
       <c r="I22"/>
       <c r="J22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K22" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M22" s="2">
         <v>43726</v>
       </c>
       <c r="N22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O22">
         <v>-28.305000400000001</v>
@@ -2486,440 +2687,440 @@
         <v>9.6863579150000003</v>
       </c>
       <c r="T22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="5">
+      <c r="A23">
         <v>573</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" t="s">
+        <v>58</v>
+      </c>
+      <c r="E23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <v>133</v>
+      </c>
+      <c r="G23" t="s">
+        <v>52</v>
+      </c>
+      <c r="H23">
+        <v>34.1</v>
+      </c>
+      <c r="J23" t="s">
         <v>59</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="5">
-        <v>133</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H23" s="5">
-        <v>34.1</v>
-      </c>
-      <c r="J23" s="5" t="s">
+      <c r="K23" t="s">
         <v>60</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="L23" t="s">
+        <v>33</v>
+      </c>
+      <c r="M23" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N23" t="s">
         <v>61</v>
       </c>
-      <c r="L23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M23" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N23" s="5" t="s">
+      <c r="O23">
+        <v>-23.17717442</v>
+      </c>
+      <c r="P23">
+        <v>45.626076859999998</v>
+      </c>
+      <c r="Q23">
+        <v>10.95872088</v>
+      </c>
+      <c r="R23">
+        <v>13.441402050000001</v>
+      </c>
+      <c r="S23">
+        <v>3.394443281</v>
+      </c>
+      <c r="T23" t="s">
         <v>62</v>
       </c>
-      <c r="O23" s="5">
-        <v>-23.17717442</v>
-      </c>
-      <c r="P23" s="5">
-        <v>45.626076859999998</v>
-      </c>
-      <c r="Q23" s="5">
-        <v>10.95872088</v>
-      </c>
-      <c r="R23" s="5">
-        <v>13.441402050000001</v>
-      </c>
-      <c r="S23" s="5">
-        <v>3.394443281</v>
-      </c>
-      <c r="T23" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="U23" s="5">
+      <c r="U23">
         <f>AVERAGE(P23:P35)</f>
         <v>44.685359341538465</v>
       </c>
-      <c r="V23" s="5">
+      <c r="V23">
         <f>AVERAGE(R23:R35)</f>
         <v>12.74586966153846</v>
       </c>
-      <c r="W23" s="5">
+      <c r="W23">
         <f>AVERAGE(S23:S35)</f>
         <v>3.5071888453846158</v>
       </c>
-      <c r="X23" s="5">
+      <c r="X23">
         <f>AVERAGE(O23:O35)</f>
         <v>-23.517025573076925</v>
       </c>
-      <c r="Y23" s="5">
+      <c r="Y23">
         <f>AVERAGE(Q23:Q35)</f>
         <v>12.132257426923079</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="5">
+      <c r="A24">
         <v>574</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" t="s">
+        <v>58</v>
+      </c>
+      <c r="E24" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24">
+        <v>25</v>
+      </c>
+      <c r="G24" t="s">
+        <v>52</v>
+      </c>
+      <c r="H24">
+        <v>0.2</v>
+      </c>
+      <c r="J24" t="s">
         <v>59</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="5">
-        <v>25</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H24" s="5">
-        <v>0.2</v>
-      </c>
-      <c r="J24" s="5" t="s">
+      <c r="K24" t="s">
         <v>60</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M24" s="6">
+      <c r="L24" t="s">
+        <v>33</v>
+      </c>
+      <c r="M24" s="2">
         <v>43690</v>
       </c>
-      <c r="N24" s="5" t="s">
+      <c r="N24" t="s">
+        <v>63</v>
+      </c>
+      <c r="O24">
+        <v>-23.64859972</v>
+      </c>
+      <c r="P24">
+        <v>41.52976658</v>
+      </c>
+      <c r="Q24">
+        <v>12.300470280000001</v>
+      </c>
+      <c r="R24">
+        <v>11.705840889999999</v>
+      </c>
+      <c r="S24">
+        <v>3.5477815700000002</v>
+      </c>
+      <c r="T24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A25">
+        <v>575</v>
+      </c>
+      <c r="B25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25">
+        <v>37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25">
+        <v>0.6</v>
+      </c>
+      <c r="J25" t="s">
+        <v>59</v>
+      </c>
+      <c r="K25" t="s">
+        <v>60</v>
+      </c>
+      <c r="L25" t="s">
+        <v>33</v>
+      </c>
+      <c r="M25" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N25" t="s">
         <v>64</v>
       </c>
-      <c r="O24" s="5">
-        <v>-23.64859972</v>
-      </c>
-      <c r="P24" s="5">
-        <v>41.52976658</v>
-      </c>
-      <c r="Q24" s="5">
-        <v>12.300470280000001</v>
-      </c>
-      <c r="R24" s="5">
-        <v>11.705840889999999</v>
-      </c>
-      <c r="S24" s="5">
-        <v>3.5477815700000002</v>
-      </c>
-      <c r="T24" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="5">
-        <v>575</v>
-      </c>
-      <c r="B25" s="5" t="s">
+      <c r="O25">
+        <v>-24.02062218</v>
+      </c>
+      <c r="P25">
+        <v>42.57560995</v>
+      </c>
+      <c r="Q25">
+        <v>11.68318616</v>
+      </c>
+      <c r="R25">
+        <v>12.200619639999999</v>
+      </c>
+      <c r="S25">
+        <v>3.4896268570000002</v>
+      </c>
+      <c r="T25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A26">
+        <v>576</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="D26" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26">
+        <v>57</v>
+      </c>
+      <c r="G26" t="s">
+        <v>52</v>
+      </c>
+      <c r="H26">
+        <v>2.4</v>
+      </c>
+      <c r="J26" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="5">
-        <v>37</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H25" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="J25" s="5" t="s">
+      <c r="K26" t="s">
         <v>60</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M25" s="6">
+      <c r="L26" t="s">
+        <v>33</v>
+      </c>
+      <c r="M26" s="2">
         <v>43690</v>
       </c>
-      <c r="N25" s="5" t="s">
+      <c r="N26" t="s">
         <v>65</v>
       </c>
-      <c r="O25" s="5">
-        <v>-24.02062218</v>
-      </c>
-      <c r="P25" s="5">
-        <v>42.57560995</v>
-      </c>
-      <c r="Q25" s="5">
-        <v>11.68318616</v>
-      </c>
-      <c r="R25" s="5">
-        <v>12.200619639999999</v>
-      </c>
-      <c r="S25" s="5">
-        <v>3.4896268570000002</v>
-      </c>
-      <c r="T25" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="5">
-        <v>576</v>
-      </c>
-      <c r="B26" s="5" t="s">
+      <c r="O26">
+        <v>-23.590532719999999</v>
+      </c>
+      <c r="P26">
+        <v>45.141289139999998</v>
+      </c>
+      <c r="Q26">
+        <v>12.29947786</v>
+      </c>
+      <c r="R26">
+        <v>13.39168214</v>
+      </c>
+      <c r="S26">
+        <v>3.370845326</v>
+      </c>
+      <c r="T26" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A27">
+        <v>577</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D26" s="5" t="s">
+      <c r="D27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27">
+        <v>46</v>
+      </c>
+      <c r="G27" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
         <v>59</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F26" s="5">
-        <v>57</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H26" s="5">
-        <v>2.4</v>
-      </c>
-      <c r="J26" s="5" t="s">
+      <c r="K27" t="s">
         <v>60</v>
       </c>
-      <c r="K26" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L26" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M26" s="6">
+      <c r="L27" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27" s="2">
         <v>43690</v>
       </c>
-      <c r="N26" s="5" t="s">
+      <c r="N27" t="s">
         <v>66</v>
       </c>
-      <c r="O26" s="5">
-        <v>-23.590532719999999</v>
-      </c>
-      <c r="P26" s="5">
-        <v>45.141289139999998</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>12.29947786</v>
-      </c>
-      <c r="R26" s="5">
-        <v>13.39168214</v>
-      </c>
-      <c r="S26" s="5">
-        <v>3.370845326</v>
-      </c>
-      <c r="T26" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A27" s="5">
-        <v>577</v>
-      </c>
-      <c r="B27" s="5" t="s">
+      <c r="O27">
+        <v>-23.616121570000001</v>
+      </c>
+      <c r="P27">
+        <v>43.545053369999998</v>
+      </c>
+      <c r="Q27">
+        <v>11.449967880000001</v>
+      </c>
+      <c r="R27">
+        <v>12.641960259999999</v>
+      </c>
+      <c r="S27">
+        <v>3.4444858599999999</v>
+      </c>
+      <c r="T27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A28">
+        <v>578</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="D28" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28">
+        <v>48</v>
+      </c>
+      <c r="G28" t="s">
+        <v>52</v>
+      </c>
+      <c r="H28">
+        <v>1.3</v>
+      </c>
+      <c r="J28" t="s">
         <v>59</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="5">
-        <v>46</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H27" s="5">
-        <v>1</v>
-      </c>
-      <c r="J27" s="5" t="s">
+      <c r="K28" t="s">
         <v>60</v>
       </c>
-      <c r="K27" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L27" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M27" s="6">
+      <c r="L28" t="s">
+        <v>33</v>
+      </c>
+      <c r="M28" s="2">
         <v>43690</v>
       </c>
-      <c r="N27" s="5" t="s">
+      <c r="N28" t="s">
         <v>67</v>
       </c>
-      <c r="O27" s="5">
-        <v>-23.616121570000001</v>
-      </c>
-      <c r="P27" s="5">
-        <v>43.545053369999998</v>
-      </c>
-      <c r="Q27" s="5">
-        <v>11.449967880000001</v>
-      </c>
-      <c r="R27" s="5">
-        <v>12.641960259999999</v>
-      </c>
-      <c r="S27" s="5">
-        <v>3.4444858599999999</v>
-      </c>
-      <c r="T27" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="5">
-        <v>578</v>
-      </c>
-      <c r="B28" s="5" t="s">
+      <c r="O28">
+        <v>-24.023574740000001</v>
+      </c>
+      <c r="P28">
+        <v>43.297679789999997</v>
+      </c>
+      <c r="Q28">
+        <v>11.973964690000001</v>
+      </c>
+      <c r="R28">
+        <v>12.81878345</v>
+      </c>
+      <c r="S28">
+        <v>3.37767464</v>
+      </c>
+      <c r="T28" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A29">
+        <v>579</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="5" t="s">
+      <c r="D29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29">
+        <v>49</v>
+      </c>
+      <c r="G29" t="s">
+        <v>52</v>
+      </c>
+      <c r="H29">
+        <v>1.6</v>
+      </c>
+      <c r="J29" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="5">
-        <v>48</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H28" s="5">
-        <v>1.3</v>
-      </c>
-      <c r="J28" s="5" t="s">
+      <c r="K29" t="s">
         <v>60</v>
       </c>
-      <c r="K28" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L28" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="6">
+      <c r="L29" t="s">
+        <v>33</v>
+      </c>
+      <c r="M29" s="2">
         <v>43690</v>
       </c>
-      <c r="N28" s="5" t="s">
+      <c r="N29" t="s">
         <v>68</v>
       </c>
-      <c r="O28" s="5">
-        <v>-24.023574740000001</v>
-      </c>
-      <c r="P28" s="5">
-        <v>43.297679789999997</v>
-      </c>
-      <c r="Q28" s="5">
-        <v>11.973964690000001</v>
-      </c>
-      <c r="R28" s="5">
-        <v>12.81878345</v>
-      </c>
-      <c r="S28" s="5">
-        <v>3.37767464</v>
-      </c>
-      <c r="T28" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="5">
-        <v>579</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F29" s="5">
-        <v>49</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H29" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L29" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M29" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N29" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="O29" s="5">
+      <c r="O29">
         <v>-24.12593013</v>
       </c>
-      <c r="P29" s="5">
+      <c r="P29">
         <v>45.66887603</v>
       </c>
-      <c r="Q29" s="5">
+      <c r="Q29">
         <v>12.48803732</v>
       </c>
-      <c r="R29" s="5">
+      <c r="R29">
         <v>12.848412639999999</v>
       </c>
-      <c r="S29" s="5">
+      <c r="S29">
         <v>3.5544372129999999</v>
       </c>
-      <c r="T29" s="5" t="s">
-        <v>63</v>
+      <c r="T29" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -2927,16 +3128,16 @@
         <v>397</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30">
         <v>246</v>
@@ -2948,20 +3149,20 @@
         <v>272.39999999999998</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J30" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K30"/>
       <c r="L30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M30" s="2">
         <v>43661</v>
       </c>
       <c r="N30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O30">
         <v>-23.10797251</v>
@@ -2979,7 +3180,7 @@
         <v>3.8218488879999999</v>
       </c>
       <c r="T30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -2987,16 +3188,16 @@
         <v>707</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F31">
         <v>46</v>
@@ -3009,17 +3210,17 @@
       </c>
       <c r="I31"/>
       <c r="J31" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K31"/>
       <c r="L31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M31" s="2">
         <v>43664</v>
       </c>
       <c r="N31" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O31">
         <v>-23.35670103</v>
@@ -3037,7 +3238,7 @@
         <v>3.441300934</v>
       </c>
       <c r="T31" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -3045,16 +3246,16 @@
         <v>708</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F32">
         <v>39</v>
@@ -3067,17 +3268,17 @@
       </c>
       <c r="I32"/>
       <c r="J32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K32"/>
       <c r="L32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M32" s="2">
         <v>43664</v>
       </c>
       <c r="N32" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O32">
         <v>-23.535163539999999</v>
@@ -3095,7 +3296,7 @@
         <v>3.5532356310000002</v>
       </c>
       <c r="T32" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -3103,16 +3304,16 @@
         <v>709</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F33">
         <v>43</v>
@@ -3125,17 +3326,17 @@
       </c>
       <c r="I33"/>
       <c r="J33" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K33"/>
       <c r="L33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M33" s="2">
         <v>43664</v>
       </c>
       <c r="N33" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O33">
         <v>-23.59037846</v>
@@ -3153,7 +3354,7 @@
         <v>3.5201942310000001</v>
       </c>
       <c r="T33" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -3161,16 +3362,16 @@
         <v>710</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F34">
         <v>42</v>
@@ -3183,17 +3384,17 @@
       </c>
       <c r="I34"/>
       <c r="J34" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K34"/>
       <c r="L34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M34" s="2">
         <v>43664</v>
       </c>
       <c r="N34" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O34">
         <v>-23.068794669999999</v>
@@ -3211,7 +3412,7 @@
         <v>3.6575420279999999</v>
       </c>
       <c r="T34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -3219,16 +3420,16 @@
         <v>711</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D35" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F35">
         <v>37</v>
@@ -3241,17 +3442,17 @@
       </c>
       <c r="I35"/>
       <c r="J35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K35"/>
       <c r="L35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M35" s="2">
         <v>43664</v>
       </c>
       <c r="N35" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O35">
         <v>-22.859766759999999</v>
@@ -3269,493 +3470,493 @@
         <v>3.4200385309999999</v>
       </c>
       <c r="T35" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A36" s="5">
+      <c r="A36">
         <v>721</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" t="s">
         <v>28</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="D36" t="s">
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36">
         <v>136</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36">
         <v>127</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36">
         <v>38</v>
       </c>
-      <c r="K36" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M36" s="6">
+      <c r="K36" t="s">
+        <v>60</v>
+      </c>
+      <c r="L36" t="s">
+        <v>33</v>
+      </c>
+      <c r="M36" s="2">
         <v>43689</v>
       </c>
-      <c r="N36" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="O36" s="5">
+      <c r="N36" t="s">
+        <v>76</v>
+      </c>
+      <c r="O36">
         <v>-23.46392457</v>
       </c>
-      <c r="P36" s="5">
+      <c r="P36">
         <v>48.387730230000003</v>
       </c>
-      <c r="Q36" s="5">
+      <c r="Q36">
         <v>13.6533783</v>
       </c>
-      <c r="R36" s="5">
+      <c r="R36">
         <v>14.85303817</v>
       </c>
-      <c r="S36" s="5">
+      <c r="S36">
         <v>3.2577665040000001</v>
       </c>
-      <c r="T36" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="U36" s="5">
+      <c r="T36" t="s">
+        <v>35</v>
+      </c>
+      <c r="U36">
         <f>AVERAGE(P36:P48)</f>
         <v>48.130241346153859</v>
       </c>
-      <c r="V36" s="5">
+      <c r="V36">
         <f>AVERAGE(R36:R48)</f>
         <v>13.736281153307694</v>
       </c>
-      <c r="W36" s="5">
+      <c r="W36">
         <f>AVERAGE(S36:S48)</f>
         <v>3.5897974680769233</v>
       </c>
-      <c r="X36" s="5">
+      <c r="X36">
         <f>AVERAGE(O36:O48)</f>
         <v>-23.615299784615388</v>
       </c>
-      <c r="Y36" s="5">
+      <c r="Y36">
         <f>AVERAGE(Q36:Q48)</f>
         <v>12.931454542307693</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A37" s="5">
+      <c r="A37">
         <v>722</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37">
+        <v>147</v>
+      </c>
+      <c r="G37">
+        <v>135</v>
+      </c>
+      <c r="H37">
+        <v>50</v>
+      </c>
+      <c r="K37" t="s">
+        <v>60</v>
+      </c>
+      <c r="L37" t="s">
+        <v>33</v>
+      </c>
+      <c r="M37" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N37" t="s">
+        <v>77</v>
+      </c>
+      <c r="O37">
+        <v>-23.579953140000001</v>
+      </c>
+      <c r="P37">
+        <v>48.145931959999999</v>
+      </c>
+      <c r="Q37">
+        <v>13.2516865</v>
+      </c>
+      <c r="R37">
+        <v>14.62314237</v>
+      </c>
+      <c r="S37">
+        <v>3.2924477350000001</v>
+      </c>
+      <c r="T37" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A38">
+        <v>798</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" t="s">
+        <v>28</v>
+      </c>
+      <c r="D38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38">
+        <v>138</v>
+      </c>
+      <c r="G38">
+        <v>130</v>
+      </c>
+      <c r="H38">
+        <v>40</v>
+      </c>
+      <c r="J38" t="s">
+        <v>83</v>
+      </c>
+      <c r="K38" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" t="s">
+        <v>33</v>
+      </c>
+      <c r="M38" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N38" t="s">
+        <v>90</v>
+      </c>
+      <c r="O38">
+        <v>-24.82197815</v>
+      </c>
+      <c r="P38">
+        <v>50.442654920000003</v>
+      </c>
+      <c r="Q38">
+        <v>13.55605458</v>
+      </c>
+      <c r="R38">
+        <v>13.864247049999999</v>
+      </c>
+      <c r="S38">
+        <v>3.6383263170000002</v>
+      </c>
+      <c r="T38" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A39">
+        <v>799</v>
+      </c>
+      <c r="B39" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" t="s">
+        <v>28</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+      <c r="E39" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39">
+        <v>147</v>
+      </c>
+      <c r="G39">
+        <v>238</v>
+      </c>
+      <c r="H39">
+        <v>47</v>
+      </c>
+      <c r="J39" t="s">
+        <v>83</v>
+      </c>
+      <c r="K39" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" t="s">
+        <v>33</v>
+      </c>
+      <c r="M39" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N39" t="s">
+        <v>91</v>
+      </c>
+      <c r="O39">
+        <v>-24.048745220000001</v>
+      </c>
+      <c r="P39">
+        <v>49.353448210000003</v>
+      </c>
+      <c r="Q39">
+        <v>12.74130587</v>
+      </c>
+      <c r="R39">
+        <v>14.41409494</v>
+      </c>
+      <c r="S39">
+        <v>3.4239713570000001</v>
+      </c>
+      <c r="T39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A40">
+        <v>800</v>
+      </c>
+      <c r="B40" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40">
+        <v>156</v>
+      </c>
+      <c r="G40">
+        <v>145</v>
+      </c>
+      <c r="H40">
+        <v>48</v>
+      </c>
+      <c r="J40" t="s">
+        <v>83</v>
+      </c>
+      <c r="K40" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" t="s">
+        <v>33</v>
+      </c>
+      <c r="M40" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N40" t="s">
+        <v>92</v>
+      </c>
+      <c r="O40">
+        <v>-23.199938060000001</v>
+      </c>
+      <c r="P40">
+        <v>46.958182299999997</v>
+      </c>
+      <c r="Q40">
+        <v>13.32790164</v>
+      </c>
+      <c r="R40">
+        <v>14.26518907</v>
+      </c>
+      <c r="S40">
+        <v>3.2918023079999998</v>
+      </c>
+      <c r="T40" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A41">
+        <v>801</v>
+      </c>
+      <c r="B41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" t="s">
+        <v>28</v>
+      </c>
+      <c r="D41" t="s">
+        <v>69</v>
+      </c>
+      <c r="E41" t="s">
+        <v>30</v>
+      </c>
+      <c r="F41" t="s">
+        <v>52</v>
+      </c>
+      <c r="G41" t="s">
+        <v>52</v>
+      </c>
+      <c r="H41" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" t="s">
+        <v>83</v>
+      </c>
+      <c r="K41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L41" t="s">
+        <v>33</v>
+      </c>
+      <c r="M41" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N41" t="s">
+        <v>94</v>
+      </c>
+      <c r="O41">
+        <v>-23.750301650000001</v>
+      </c>
+      <c r="P41">
+        <v>47.341653639999997</v>
+      </c>
+      <c r="Q41">
+        <v>12.46836497</v>
+      </c>
+      <c r="R41">
+        <v>13.628827510000001</v>
+      </c>
+      <c r="S41">
+        <v>3.4736409730000002</v>
+      </c>
+      <c r="T41" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A42">
+        <v>857</v>
+      </c>
+      <c r="B42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" t="s">
+        <v>69</v>
+      </c>
+      <c r="E42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F42">
+        <v>68</v>
+      </c>
+      <c r="G42" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42">
+        <v>4</v>
+      </c>
+      <c r="J42" t="s">
+        <v>99</v>
+      </c>
+      <c r="K42" t="s">
+        <v>60</v>
+      </c>
+      <c r="L42" t="s">
+        <v>33</v>
+      </c>
+      <c r="M42" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N42" t="s">
+        <v>100</v>
+      </c>
+      <c r="O42">
+        <v>-23.99557239</v>
+      </c>
+      <c r="P42">
+        <v>45.834344119999997</v>
+      </c>
+      <c r="Q42">
+        <v>12.90011838</v>
+      </c>
+      <c r="R42">
+        <v>13.68383482</v>
+      </c>
+      <c r="S42">
+        <v>3.3495248009999998</v>
+      </c>
+      <c r="T42" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A43">
+        <v>858</v>
+      </c>
+      <c r="B43" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" t="s">
+        <v>28</v>
+      </c>
+      <c r="D43" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43">
         <v>70</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" s="5">
-        <v>147</v>
-      </c>
-      <c r="G37" s="5">
-        <v>135</v>
-      </c>
-      <c r="H37" s="5">
-        <v>50</v>
-      </c>
-      <c r="K37" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L37" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M37" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N37" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="O37" s="5">
-        <v>-23.579953140000001</v>
-      </c>
-      <c r="P37" s="5">
-        <v>48.145931959999999</v>
-      </c>
-      <c r="Q37" s="5">
-        <v>13.2516865</v>
-      </c>
-      <c r="R37" s="5">
-        <v>14.62314237</v>
-      </c>
-      <c r="S37" s="5">
-        <v>3.2924477350000001</v>
-      </c>
-      <c r="T37" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A38" s="5">
-        <v>798</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" s="5">
-        <v>138</v>
-      </c>
-      <c r="G38" s="5">
-        <v>130</v>
-      </c>
-      <c r="H38" s="5">
-        <v>40</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K38" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L38" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M38" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N38" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="O38" s="5">
-        <v>-24.82197815</v>
-      </c>
-      <c r="P38" s="5">
-        <v>50.442654920000003</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>13.55605458</v>
-      </c>
-      <c r="R38" s="5">
-        <v>13.864247049999999</v>
-      </c>
-      <c r="S38" s="5">
-        <v>3.6383263170000002</v>
-      </c>
-      <c r="T38" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A39" s="5">
-        <v>799</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="5">
-        <v>147</v>
-      </c>
-      <c r="G39" s="5">
-        <v>238</v>
-      </c>
-      <c r="H39" s="5">
-        <v>47</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L39" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M39" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N39" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="O39" s="5">
-        <v>-24.048745220000001</v>
-      </c>
-      <c r="P39" s="5">
-        <v>49.353448210000003</v>
-      </c>
-      <c r="Q39" s="5">
-        <v>12.74130587</v>
-      </c>
-      <c r="R39" s="5">
-        <v>14.41409494</v>
-      </c>
-      <c r="S39" s="5">
-        <v>3.4239713570000001</v>
-      </c>
-      <c r="T39" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A40" s="5">
-        <v>800</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" s="5">
-        <v>156</v>
-      </c>
-      <c r="G40" s="5">
-        <v>145</v>
-      </c>
-      <c r="H40" s="5">
-        <v>48</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L40" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M40" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N40" s="5" t="s">
+      <c r="G43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43">
+        <v>4</v>
+      </c>
+      <c r="J43" t="s">
+        <v>99</v>
+      </c>
+      <c r="K43" t="s">
+        <v>60</v>
+      </c>
+      <c r="L43" t="s">
+        <v>33</v>
+      </c>
+      <c r="M43" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N43" t="s">
+        <v>101</v>
+      </c>
+      <c r="O43">
+        <v>-23.983607960000001</v>
+      </c>
+      <c r="P43">
+        <v>45.891883290000003</v>
+      </c>
+      <c r="Q43">
+        <v>12.33139493</v>
+      </c>
+      <c r="R43">
+        <v>14.02760546</v>
+      </c>
+      <c r="S43">
+        <v>3.2715407779999999</v>
+      </c>
+      <c r="T43" t="s">
         <v>93</v>
-      </c>
-      <c r="O40" s="5">
-        <v>-23.199938060000001</v>
-      </c>
-      <c r="P40" s="5">
-        <v>46.958182299999997</v>
-      </c>
-      <c r="Q40" s="5">
-        <v>13.32790164</v>
-      </c>
-      <c r="R40" s="5">
-        <v>14.26518907</v>
-      </c>
-      <c r="S40" s="5">
-        <v>3.2918023079999998</v>
-      </c>
-      <c r="T40" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A41" s="5">
-        <v>801</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K41" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L41" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M41" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N41" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="O41" s="5">
-        <v>-23.750301650000001</v>
-      </c>
-      <c r="P41" s="5">
-        <v>47.341653639999997</v>
-      </c>
-      <c r="Q41" s="5">
-        <v>12.46836497</v>
-      </c>
-      <c r="R41" s="5">
-        <v>13.628827510000001</v>
-      </c>
-      <c r="S41" s="5">
-        <v>3.4736409730000002</v>
-      </c>
-      <c r="T41" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A42" s="5">
-        <v>857</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F42" s="5">
-        <v>68</v>
-      </c>
-      <c r="G42" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H42" s="5">
-        <v>4</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M42" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="O42" s="5">
-        <v>-23.99557239</v>
-      </c>
-      <c r="P42" s="5">
-        <v>45.834344119999997</v>
-      </c>
-      <c r="Q42" s="5">
-        <v>12.90011838</v>
-      </c>
-      <c r="R42" s="5">
-        <v>13.68383482</v>
-      </c>
-      <c r="S42" s="5">
-        <v>3.3495248009999998</v>
-      </c>
-      <c r="T42" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A43" s="5">
-        <v>858</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" s="5">
-        <v>70</v>
-      </c>
-      <c r="G43" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H43" s="5">
-        <v>4</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="K43" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L43" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M43" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N43" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="O43" s="5">
-        <v>-23.983607960000001</v>
-      </c>
-      <c r="P43" s="5">
-        <v>45.891883290000003</v>
-      </c>
-      <c r="Q43" s="5">
-        <v>12.33139493</v>
-      </c>
-      <c r="R43" s="5">
-        <v>14.02760546</v>
-      </c>
-      <c r="S43" s="5">
-        <v>3.2715407779999999</v>
-      </c>
-      <c r="T43" s="5" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:25" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
@@ -3763,16 +3964,16 @@
         <v>595</v>
       </c>
       <c r="B44" t="s">
+        <v>27</v>
+      </c>
+      <c r="C44" t="s">
         <v>28</v>
       </c>
-      <c r="C44" t="s">
-        <v>29</v>
-      </c>
       <c r="D44" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44">
         <v>136</v>
@@ -3784,22 +3985,22 @@
         <v>35</v>
       </c>
       <c r="I44" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L44" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M44" s="2">
         <v>43725</v>
       </c>
       <c r="N44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O44">
         <v>-22.611267229999999</v>
@@ -3817,24 +4018,24 @@
         <v>3.2440325310000002</v>
       </c>
       <c r="T44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>596</v>
       </c>
       <c r="B45" t="s">
+        <v>27</v>
+      </c>
+      <c r="C45" t="s">
         <v>28</v>
       </c>
-      <c r="C45" t="s">
-        <v>29</v>
-      </c>
       <c r="D45" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F45">
         <v>139</v>
@@ -3846,22 +4047,22 @@
         <v>32.4</v>
       </c>
       <c r="I45" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J45" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K45" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L45" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M45" s="2">
         <v>43725</v>
       </c>
       <c r="N45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O45">
         <v>-22.955732480000002</v>
@@ -3879,24 +4080,24 @@
         <v>3.2620868490000001</v>
       </c>
       <c r="T45" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>859</v>
       </c>
       <c r="B46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" t="s">
         <v>28</v>
       </c>
-      <c r="C46" t="s">
-        <v>29</v>
-      </c>
       <c r="D46" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46">
         <v>72</v>
@@ -3908,16 +4109,16 @@
         <v>5</v>
       </c>
       <c r="J46" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M46" s="2">
         <v>43609</v>
       </c>
       <c r="N46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O46">
         <v>-24.21392316</v>
@@ -3935,45 +4136,45 @@
         <v>3.382593038</v>
       </c>
       <c r="T46" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>860</v>
       </c>
       <c r="B47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" t="s">
         <v>28</v>
       </c>
-      <c r="C47" t="s">
-        <v>29</v>
-      </c>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F47">
         <v>64</v>
       </c>
       <c r="G47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H47">
         <v>3</v>
       </c>
       <c r="J47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L47" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M47" s="2">
         <v>43609</v>
       </c>
       <c r="N47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O47">
         <v>-23.700449880000001</v>
@@ -3991,24 +4192,24 @@
         <v>3.2982339540000001</v>
       </c>
       <c r="T47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>863</v>
       </c>
       <c r="B48" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" t="s">
         <v>28</v>
       </c>
-      <c r="C48" t="s">
+      <c r="D48" t="s">
         <v>29</v>
       </c>
-      <c r="D48" t="s">
-        <v>30</v>
-      </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F48">
         <v>409</v>
@@ -4020,16 +4221,16 @@
         <v>899</v>
       </c>
       <c r="J48" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L48" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M48" s="2">
         <v>43628</v>
       </c>
       <c r="N48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O48">
         <v>-22.673503310000001</v>
@@ -4047,24 +4248,24 @@
         <v>6.4813999400000002</v>
       </c>
       <c r="T48" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>865</v>
       </c>
       <c r="B49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" t="s">
         <v>28</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>29</v>
       </c>
-      <c r="D49" t="s">
-        <v>30</v>
-      </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F49">
         <v>391</v>
@@ -4076,16 +4277,16 @@
         <v>925</v>
       </c>
       <c r="J49" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L49" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M49" s="2">
         <v>43634</v>
       </c>
       <c r="N49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O49">
         <v>-25.265795619999999</v>
@@ -4103,24 +4304,24 @@
         <v>9.4880931870000005</v>
       </c>
       <c r="T49" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>866</v>
       </c>
       <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>29</v>
       </c>
-      <c r="D50" t="s">
-        <v>30</v>
-      </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F50">
         <v>380</v>
@@ -4132,16 +4333,16 @@
         <v>696</v>
       </c>
       <c r="J50" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M50" s="2">
         <v>43634</v>
       </c>
       <c r="N50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O50">
         <v>-24.93079169</v>
@@ -4159,24 +4360,24 @@
         <v>6.2910516019999996</v>
       </c>
       <c r="T50" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>597</v>
       </c>
       <c r="B51" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" t="s">
         <v>28</v>
       </c>
-      <c r="C51" t="s">
-        <v>29</v>
-      </c>
       <c r="D51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F51">
         <v>141</v>
@@ -4188,22 +4389,22 @@
         <v>33.4</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L51" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M51" s="2">
         <v>43725</v>
       </c>
       <c r="N51" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O51">
         <v>-22.6860654</v>
@@ -4221,24 +4422,24 @@
         <v>3.4097823009999999</v>
       </c>
       <c r="T51" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>598</v>
       </c>
       <c r="B52" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" t="s">
         <v>28</v>
       </c>
-      <c r="C52" t="s">
-        <v>29</v>
-      </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F52">
         <v>162</v>
@@ -4250,22 +4451,22 @@
         <v>58</v>
       </c>
       <c r="I52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K52" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L52" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M52" s="2">
         <v>43725</v>
       </c>
       <c r="N52" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="O52">
         <v>-22.44100298</v>
@@ -4283,24 +4484,24 @@
         <v>3.5500469479999999</v>
       </c>
       <c r="T52" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>599</v>
       </c>
       <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" t="s">
         <v>28</v>
       </c>
-      <c r="C53" t="s">
-        <v>29</v>
-      </c>
       <c r="D53" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F53">
         <v>168</v>
@@ -4312,22 +4513,22 @@
         <v>63.6</v>
       </c>
       <c r="I53" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L53" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M53" s="2">
         <v>43725</v>
       </c>
       <c r="N53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O53">
         <v>-22.47446532</v>
@@ -4345,24 +4546,24 @@
         <v>3.3075288430000001</v>
       </c>
       <c r="T53" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>664</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E54" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F54">
         <v>42</v>
@@ -4374,16 +4575,16 @@
         <v>0.6</v>
       </c>
       <c r="J54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M54" s="2">
         <v>43661</v>
       </c>
       <c r="N54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="O54">
         <v>-25.403596960000002</v>
@@ -4401,45 +4602,45 @@
         <v>3.4211627249999998</v>
       </c>
       <c r="T54" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>915</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F55">
         <v>50</v>
       </c>
       <c r="G55" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H55">
         <v>1</v>
       </c>
       <c r="J55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M55" s="2">
         <v>43664</v>
       </c>
       <c r="N55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O55">
         <v>-24.113320229999999</v>
@@ -4457,45 +4658,45 @@
         <v>3.4652416270000002</v>
       </c>
       <c r="T55" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>916</v>
       </c>
       <c r="B56" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F56">
         <v>49</v>
       </c>
       <c r="G56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H56">
         <v>4</v>
       </c>
       <c r="J56" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M56" s="2">
         <v>43664</v>
       </c>
       <c r="N56" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O56">
         <v>-24.704693989999999</v>
@@ -4513,24 +4714,24 @@
         <v>3.3929902009999999</v>
       </c>
       <c r="T56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>310</v>
       </c>
       <c r="B57" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C57" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D57" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E57" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F57">
         <v>232</v>
@@ -4542,19 +4743,19 @@
         <v>193.6</v>
       </c>
       <c r="I57" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J57" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M57" s="2">
         <v>43606</v>
       </c>
       <c r="N57" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O57">
         <v>-23.005767290000001</v>
@@ -4572,45 +4773,45 @@
         <v>3.3974636380000001</v>
       </c>
       <c r="T57" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>917</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C58" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E58" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F58">
         <v>44</v>
       </c>
       <c r="G58" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="J58" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M58" s="2">
         <v>43664</v>
       </c>
       <c r="N58" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="O58">
         <v>-24.1887303</v>
@@ -4628,24 +4829,24 @@
         <v>3.5833358450000001</v>
       </c>
       <c r="T58" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>401</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C59" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E59" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F59">
         <v>204</v>
@@ -4657,16 +4858,16 @@
         <v>93</v>
       </c>
       <c r="J59" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M59" s="2">
         <v>43609</v>
       </c>
       <c r="N59" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="O59">
         <v>-21.509138140000001</v>
@@ -4684,24 +4885,24 @@
         <v>3.2111317279999998</v>
       </c>
       <c r="T59" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>402</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C60" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E60" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F60">
         <v>214</v>
@@ -4713,16 +4914,16 @@
         <v>108</v>
       </c>
       <c r="J60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M60" s="2">
         <v>43609</v>
       </c>
       <c r="N60" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O60">
         <v>-21.641882689999999</v>
@@ -4740,24 +4941,24 @@
         <v>3.1931089020000001</v>
       </c>
       <c r="T60" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="61" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>427</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C61" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E61" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F61">
         <v>227</v>
@@ -4769,19 +4970,19 @@
         <v>134.80000000000001</v>
       </c>
       <c r="I61" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J61" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L61" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M61" s="2">
         <v>43609</v>
       </c>
       <c r="N61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O61">
         <v>-21.411928230000001</v>
@@ -4799,24 +5000,24 @@
         <v>3.2081793529999998</v>
       </c>
       <c r="T61" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="62" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>428</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F62">
         <v>229</v>
@@ -4828,19 +5029,19 @@
         <v>131.19999999999999</v>
       </c>
       <c r="I62" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J62" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M62" s="2">
         <v>43609</v>
       </c>
       <c r="N62" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="O62">
         <v>-21.608923619999999</v>
@@ -4858,24 +5059,24 @@
         <v>3.243647079</v>
       </c>
       <c r="T62" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="63" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>429</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C63" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F63">
         <v>232</v>
@@ -4887,19 +5088,19 @@
         <v>138.5</v>
       </c>
       <c r="I63" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J63" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M63" s="2">
         <v>43609</v>
       </c>
       <c r="N63" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O63">
         <v>-21.12332997</v>
@@ -4917,24 +5118,24 @@
         <v>3.2026293400000001</v>
       </c>
       <c r="T63" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="64" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>438</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D64" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F64">
         <v>219</v>
@@ -4946,19 +5147,19 @@
         <v>192.1</v>
       </c>
       <c r="I64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J64" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M64" s="2">
         <v>43611</v>
       </c>
       <c r="N64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O64">
         <v>-22.541696810000001</v>
@@ -4976,24 +5177,24 @@
         <v>3.2945222919999999</v>
       </c>
       <c r="T64" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>439</v>
       </c>
       <c r="B65" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C65" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D65" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F65">
         <v>243</v>
@@ -5005,19 +5206,19 @@
         <v>226.7</v>
       </c>
       <c r="I65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J65" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M65" s="2">
         <v>43611</v>
       </c>
       <c r="N65" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="O65">
         <v>-23.71480438</v>
@@ -5035,24 +5236,24 @@
         <v>3.775828121</v>
       </c>
       <c r="T65" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>455</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C66" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D66" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E66" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F66">
         <v>241</v>
@@ -5064,19 +5265,19 @@
         <v>219.7</v>
       </c>
       <c r="I66" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J66" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M66" s="2">
         <v>43606</v>
       </c>
       <c r="N66" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O66">
         <v>-22.9396275</v>
@@ -5094,24 +5295,24 @@
         <v>3.4360559959999999</v>
       </c>
       <c r="T66" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>465</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D67" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F67">
         <v>299</v>
@@ -5123,19 +5324,19 @@
         <v>517.9</v>
       </c>
       <c r="I67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J67" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M67" s="2">
         <v>43609</v>
       </c>
       <c r="N67" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="O67">
         <v>-22.622464919999999</v>
@@ -5153,24 +5354,24 @@
         <v>3.356948901</v>
       </c>
       <c r="T67" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>466</v>
       </c>
       <c r="B68" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C68" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D68" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F68">
         <v>284</v>
@@ -5182,19 +5383,19 @@
         <v>416.7</v>
       </c>
       <c r="I68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J68" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L68" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M68" s="2">
         <v>43609</v>
       </c>
       <c r="N68" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O68">
         <v>-24.893821809999999</v>
@@ -5212,48 +5413,48 @@
         <v>4.8028558700000001</v>
       </c>
       <c r="T68" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>476</v>
       </c>
       <c r="B69" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C69" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E69" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F69">
         <v>296</v>
       </c>
       <c r="G69" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H69">
         <v>182</v>
       </c>
       <c r="I69" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J69" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M69" s="2">
         <v>43606</v>
       </c>
       <c r="N69" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O69">
         <v>-22.341003990000001</v>
@@ -5271,575 +5472,575 @@
         <v>3.2566375540000001</v>
       </c>
       <c r="T69" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A70" s="5">
+      <c r="A70">
         <v>762</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F70" s="5">
+      <c r="D70" t="s">
+        <v>41</v>
+      </c>
+      <c r="E70" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70">
         <v>179</v>
       </c>
-      <c r="G70" s="5">
+      <c r="G70">
         <v>169</v>
       </c>
-      <c r="H70" s="5">
+      <c r="H70">
         <v>74</v>
       </c>
-      <c r="J70" s="5" t="s">
+      <c r="J70" t="s">
+        <v>83</v>
+      </c>
+      <c r="K70" t="s">
+        <v>60</v>
+      </c>
+      <c r="L70" t="s">
+        <v>33</v>
+      </c>
+      <c r="M70" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N70" t="s">
         <v>84</v>
       </c>
-      <c r="K70" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L70" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M70" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N70" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="O70" s="5">
+      <c r="O70">
         <v>-23.325142140000001</v>
       </c>
-      <c r="P70" s="5">
+      <c r="P70">
         <v>46.129466020000002</v>
       </c>
-      <c r="Q70" s="5">
+      <c r="Q70">
         <v>14.255814640000001</v>
       </c>
-      <c r="R70" s="5">
+      <c r="R70">
         <v>14.09803449</v>
       </c>
-      <c r="S70" s="5">
+      <c r="S70">
         <v>3.272049451</v>
       </c>
-      <c r="T70" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="U70" s="5">
+      <c r="T70" t="s">
+        <v>80</v>
+      </c>
+      <c r="U70">
         <f>AVERAGE(P70:P82)</f>
         <v>44.849519902307684</v>
       </c>
-      <c r="V70" s="5">
+      <c r="V70">
         <f>AVERAGE(R70:R82)</f>
         <v>13.606231183461539</v>
       </c>
-      <c r="W70" s="5">
+      <c r="W70">
         <f>AVERAGE(S70:S82)</f>
         <v>3.2911418164615389</v>
       </c>
-      <c r="X70" s="5">
+      <c r="X70">
         <f>AVERAGE(O70:O82)</f>
         <v>-22.957768973076927</v>
       </c>
-      <c r="Y70" s="5">
+      <c r="Y70">
         <f>AVERAGE(Q70:Q82)</f>
         <v>13.280494286923076</v>
       </c>
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A71" s="5">
+      <c r="A71">
         <v>763</v>
       </c>
-      <c r="B71" s="5" t="s">
+      <c r="B71" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" t="s">
         <v>28</v>
       </c>
-      <c r="C71" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F71" s="5">
+      <c r="D71" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" t="s">
+        <v>30</v>
+      </c>
+      <c r="F71">
         <v>200</v>
       </c>
-      <c r="G71" s="5">
+      <c r="G71">
         <v>188</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H71">
         <v>125</v>
       </c>
-      <c r="J71" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K71" s="5" t="s">
+      <c r="J71" t="s">
+        <v>83</v>
+      </c>
+      <c r="K71" t="s">
+        <v>60</v>
+      </c>
+      <c r="L71" t="s">
+        <v>33</v>
+      </c>
+      <c r="M71" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N71" t="s">
+        <v>85</v>
+      </c>
+      <c r="O71">
+        <v>-23.20305273</v>
+      </c>
+      <c r="P71">
+        <v>45.948652680000002</v>
+      </c>
+      <c r="Q71">
+        <v>14.546726120000001</v>
+      </c>
+      <c r="R71">
+        <v>14.0645959</v>
+      </c>
+      <c r="S71">
+        <v>3.2669728309999999</v>
+      </c>
+      <c r="T71" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>764</v>
+      </c>
+      <c r="B72" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="s">
+        <v>41</v>
+      </c>
+      <c r="E72" t="s">
+        <v>30</v>
+      </c>
+      <c r="F72">
+        <v>183</v>
+      </c>
+      <c r="G72">
+        <v>174</v>
+      </c>
+      <c r="H72">
+        <v>88</v>
+      </c>
+      <c r="J72" t="s">
+        <v>83</v>
+      </c>
+      <c r="K72" t="s">
+        <v>60</v>
+      </c>
+      <c r="L72" t="s">
+        <v>33</v>
+      </c>
+      <c r="M72" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N72" t="s">
+        <v>86</v>
+      </c>
+      <c r="O72">
+        <v>-23.27154191</v>
+      </c>
+      <c r="P72">
+        <v>47.342575619999998</v>
+      </c>
+      <c r="Q72">
+        <v>15.07252897</v>
+      </c>
+      <c r="R72">
+        <v>13.94331094</v>
+      </c>
+      <c r="S72">
+        <v>3.395361104</v>
+      </c>
+      <c r="T72" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>765</v>
+      </c>
+      <c r="B73" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" t="s">
+        <v>28</v>
+      </c>
+      <c r="D73" t="s">
+        <v>41</v>
+      </c>
+      <c r="E73" t="s">
+        <v>30</v>
+      </c>
+      <c r="F73">
+        <v>178</v>
+      </c>
+      <c r="G73">
+        <v>169</v>
+      </c>
+      <c r="H73">
+        <v>76</v>
+      </c>
+      <c r="J73" t="s">
+        <v>83</v>
+      </c>
+      <c r="K73" t="s">
+        <v>60</v>
+      </c>
+      <c r="L73" t="s">
+        <v>33</v>
+      </c>
+      <c r="M73" s="2">
+        <v>43689</v>
+      </c>
+      <c r="N73" t="s">
+        <v>87</v>
+      </c>
+      <c r="O73">
+        <v>-23.3688164</v>
+      </c>
+      <c r="P73">
+        <v>46.007942489999998</v>
+      </c>
+      <c r="Q73">
+        <v>13.41453008</v>
+      </c>
+      <c r="R73">
+        <v>14.018046999999999</v>
+      </c>
+      <c r="S73">
+        <v>3.2820508089999998</v>
+      </c>
+      <c r="T73" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>924</v>
+      </c>
+      <c r="B74" t="s">
+        <v>27</v>
+      </c>
+      <c r="C74" t="s">
+        <v>28</v>
+      </c>
+      <c r="D74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" t="s">
+        <v>30</v>
+      </c>
+      <c r="F74">
+        <v>62</v>
+      </c>
+      <c r="G74" t="s">
+        <v>52</v>
+      </c>
+      <c r="H74">
+        <v>2</v>
+      </c>
+      <c r="J74" t="s">
+        <v>110</v>
+      </c>
+      <c r="K74" t="s">
+        <v>60</v>
+      </c>
+      <c r="L74" t="s">
+        <v>33</v>
+      </c>
+      <c r="M74" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N74" t="s">
+        <v>111</v>
+      </c>
+      <c r="O74">
+        <v>-23.939678600000001</v>
+      </c>
+      <c r="P74">
+        <v>47.670220700000002</v>
+      </c>
+      <c r="Q74">
+        <v>11.638315739999999</v>
+      </c>
+      <c r="R74">
+        <v>14.34697708</v>
+      </c>
+      <c r="S74">
+        <v>3.3226665400000002</v>
+      </c>
+      <c r="T74" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>925</v>
+      </c>
+      <c r="B75" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" t="s">
+        <v>28</v>
+      </c>
+      <c r="D75" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" t="s">
+        <v>30</v>
+      </c>
+      <c r="F75">
+        <v>65</v>
+      </c>
+      <c r="G75" t="s">
+        <v>52</v>
+      </c>
+      <c r="H75">
+        <v>3</v>
+      </c>
+      <c r="J75" t="s">
+        <v>110</v>
+      </c>
+      <c r="K75" t="s">
+        <v>60</v>
+      </c>
+      <c r="L75" t="s">
+        <v>33</v>
+      </c>
+      <c r="M75" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N75" t="s">
+        <v>113</v>
+      </c>
+      <c r="O75">
+        <v>-23.81366439</v>
+      </c>
+      <c r="P75">
+        <v>45.028628789999999</v>
+      </c>
+      <c r="Q75">
+        <v>12.71220741</v>
+      </c>
+      <c r="R75">
+        <v>12.763345879999999</v>
+      </c>
+      <c r="S75">
+        <v>3.527964313</v>
+      </c>
+      <c r="T75" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>926</v>
+      </c>
+      <c r="B76" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" t="s">
+        <v>28</v>
+      </c>
+      <c r="D76" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" t="s">
+        <v>30</v>
+      </c>
+      <c r="F76">
         <v>61</v>
       </c>
-      <c r="L71" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M71" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N71" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="O71" s="5">
-        <v>-23.20305273</v>
-      </c>
-      <c r="P71" s="5">
-        <v>45.948652680000002</v>
-      </c>
-      <c r="Q71" s="5">
-        <v>14.546726120000001</v>
-      </c>
-      <c r="R71" s="5">
-        <v>14.0645959</v>
-      </c>
-      <c r="S71" s="5">
-        <v>3.2669728309999999</v>
-      </c>
-      <c r="T71" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A72" s="5">
-        <v>764</v>
-      </c>
-      <c r="B72" s="5" t="s">
+      <c r="G76" t="s">
+        <v>52</v>
+      </c>
+      <c r="H76">
+        <v>2</v>
+      </c>
+      <c r="J76" t="s">
+        <v>110</v>
+      </c>
+      <c r="K76" t="s">
+        <v>60</v>
+      </c>
+      <c r="L76" t="s">
+        <v>33</v>
+      </c>
+      <c r="M76" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N76" t="s">
+        <v>114</v>
+      </c>
+      <c r="O76">
+        <v>-24.05477819</v>
+      </c>
+      <c r="P76">
+        <v>47.183808130000003</v>
+      </c>
+      <c r="Q76">
+        <v>12.43806427</v>
+      </c>
+      <c r="R76">
+        <v>13.995686040000001</v>
+      </c>
+      <c r="S76">
+        <v>3.3713108439999999</v>
+      </c>
+      <c r="T76" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>927</v>
+      </c>
+      <c r="B77" t="s">
+        <v>27</v>
+      </c>
+      <c r="C77" t="s">
         <v>28</v>
       </c>
-      <c r="C72" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D72" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F72" s="5">
-        <v>183</v>
-      </c>
-      <c r="G72" s="5">
-        <v>174</v>
-      </c>
-      <c r="H72" s="5">
-        <v>88</v>
-      </c>
-      <c r="J72" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L72" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M72" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N72" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="O72" s="5">
-        <v>-23.27154191</v>
-      </c>
-      <c r="P72" s="5">
-        <v>47.342575619999998</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>15.07252897</v>
-      </c>
-      <c r="R72" s="5">
-        <v>13.94331094</v>
-      </c>
-      <c r="S72" s="5">
-        <v>3.395361104</v>
-      </c>
-      <c r="T72" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A73" s="5">
-        <v>765</v>
-      </c>
-      <c r="B73" s="5" t="s">
+      <c r="D77" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" t="s">
+        <v>30</v>
+      </c>
+      <c r="F77">
+        <v>59</v>
+      </c>
+      <c r="G77" t="s">
+        <v>52</v>
+      </c>
+      <c r="H77">
+        <v>2</v>
+      </c>
+      <c r="J77" t="s">
+        <v>110</v>
+      </c>
+      <c r="K77" t="s">
+        <v>60</v>
+      </c>
+      <c r="L77" t="s">
+        <v>33</v>
+      </c>
+      <c r="M77" s="2">
+        <v>43690</v>
+      </c>
+      <c r="N77" t="s">
+        <v>115</v>
+      </c>
+      <c r="O77">
+        <v>-23.886097759999998</v>
+      </c>
+      <c r="P77">
+        <v>46.820824039999998</v>
+      </c>
+      <c r="Q77">
+        <v>12.58401098</v>
+      </c>
+      <c r="R77">
+        <v>14.28768788</v>
+      </c>
+      <c r="S77">
+        <v>3.2770049609999998</v>
+      </c>
+      <c r="T77" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>928</v>
+      </c>
+      <c r="B78" t="s">
+        <v>27</v>
+      </c>
+      <c r="C78" t="s">
         <v>28</v>
       </c>
-      <c r="C73" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D73" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F73" s="5">
-        <v>178</v>
-      </c>
-      <c r="G73" s="5">
-        <v>169</v>
-      </c>
-      <c r="H73" s="5">
-        <v>76</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="K73" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L73" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M73" s="6">
-        <v>43689</v>
-      </c>
-      <c r="N73" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="O73" s="5">
-        <v>-23.3688164</v>
-      </c>
-      <c r="P73" s="5">
-        <v>46.007942489999998</v>
-      </c>
-      <c r="Q73" s="5">
-        <v>13.41453008</v>
-      </c>
-      <c r="R73" s="5">
-        <v>14.018046999999999</v>
-      </c>
-      <c r="S73" s="5">
-        <v>3.2820508089999998</v>
-      </c>
-      <c r="T73" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A74" s="5">
-        <v>924</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F74" s="5">
-        <v>62</v>
-      </c>
-      <c r="G74" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H74" s="5">
-        <v>2</v>
-      </c>
-      <c r="J74" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K74" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L74" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M74" s="6">
+      <c r="D78" t="s">
+        <v>41</v>
+      </c>
+      <c r="E78" t="s">
+        <v>30</v>
+      </c>
+      <c r="F78">
+        <v>66</v>
+      </c>
+      <c r="G78" t="s">
+        <v>52</v>
+      </c>
+      <c r="H78">
+        <v>3</v>
+      </c>
+      <c r="J78" t="s">
+        <v>110</v>
+      </c>
+      <c r="K78" t="s">
+        <v>60</v>
+      </c>
+      <c r="L78" t="s">
+        <v>33</v>
+      </c>
+      <c r="M78" s="2">
         <v>43690</v>
       </c>
-      <c r="N74" s="5" t="s">
+      <c r="N78" t="s">
+        <v>116</v>
+      </c>
+      <c r="O78">
+        <v>-23.667805430000001</v>
+      </c>
+      <c r="P78">
+        <v>46.89896452</v>
+      </c>
+      <c r="Q78">
+        <v>11.608731949999999</v>
+      </c>
+      <c r="R78">
+        <v>14.184562039999999</v>
+      </c>
+      <c r="S78">
+        <v>3.306338566</v>
+      </c>
+      <c r="T78" t="s">
         <v>112</v>
       </c>
-      <c r="O74" s="5">
-        <v>-23.939678600000001</v>
-      </c>
-      <c r="P74" s="5">
-        <v>47.670220700000002</v>
-      </c>
-      <c r="Q74" s="5">
-        <v>11.638315739999999</v>
-      </c>
-      <c r="R74" s="5">
-        <v>14.34697708</v>
-      </c>
-      <c r="S74" s="5">
-        <v>3.3226665400000002</v>
-      </c>
-      <c r="T74" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A75" s="5">
-        <v>925</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F75" s="5">
-        <v>65</v>
-      </c>
-      <c r="G75" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" s="5">
-        <v>3</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K75" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L75" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M75" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N75" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="O75" s="5">
-        <v>-23.81366439</v>
-      </c>
-      <c r="P75" s="5">
-        <v>45.028628789999999</v>
-      </c>
-      <c r="Q75" s="5">
-        <v>12.71220741</v>
-      </c>
-      <c r="R75" s="5">
-        <v>12.763345879999999</v>
-      </c>
-      <c r="S75" s="5">
-        <v>3.527964313</v>
-      </c>
-      <c r="T75" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A76" s="5">
-        <v>926</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D76" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F76" s="5">
-        <v>61</v>
-      </c>
-      <c r="G76" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H76" s="5">
-        <v>2</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L76" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M76" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N76" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="O76" s="5">
-        <v>-24.05477819</v>
-      </c>
-      <c r="P76" s="5">
-        <v>47.183808130000003</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>12.43806427</v>
-      </c>
-      <c r="R76" s="5">
-        <v>13.995686040000001</v>
-      </c>
-      <c r="S76" s="5">
-        <v>3.3713108439999999</v>
-      </c>
-      <c r="T76" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A77" s="5">
-        <v>927</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D77" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F77" s="5">
-        <v>59</v>
-      </c>
-      <c r="G77" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H77" s="5">
-        <v>2</v>
-      </c>
-      <c r="J77" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K77" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L77" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M77" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N77" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="O77" s="5">
-        <v>-23.886097759999998</v>
-      </c>
-      <c r="P77" s="5">
-        <v>46.820824039999998</v>
-      </c>
-      <c r="Q77" s="5">
-        <v>12.58401098</v>
-      </c>
-      <c r="R77" s="5">
-        <v>14.28768788</v>
-      </c>
-      <c r="S77" s="5">
-        <v>3.2770049609999998</v>
-      </c>
-      <c r="T77" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A78" s="5">
-        <v>928</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D78" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F78" s="5">
-        <v>66</v>
-      </c>
-      <c r="G78" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="H78" s="5">
-        <v>3</v>
-      </c>
-      <c r="J78" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="K78" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L78" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="M78" s="6">
-        <v>43690</v>
-      </c>
-      <c r="N78" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="O78" s="5">
-        <v>-23.667805430000001</v>
-      </c>
-      <c r="P78" s="5">
-        <v>46.89896452</v>
-      </c>
-      <c r="Q78" s="5">
-        <v>11.608731949999999</v>
-      </c>
-      <c r="R78" s="5">
-        <v>14.184562039999999</v>
-      </c>
-      <c r="S78" s="5">
-        <v>3.306338566</v>
-      </c>
-      <c r="T78" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="79" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>410</v>
       </c>
       <c r="B79" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" t="s">
         <v>28</v>
       </c>
-      <c r="C79" t="s">
-        <v>29</v>
-      </c>
       <c r="D79" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E79" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F79">
         <v>262</v>
@@ -5851,19 +6052,19 @@
         <v>234</v>
       </c>
       <c r="I79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J79" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L79" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M79" s="2">
         <v>43724</v>
       </c>
       <c r="N79" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="O79">
         <v>-20.974598449999998</v>
@@ -5881,24 +6082,24 @@
         <v>3.1663611010000001</v>
       </c>
       <c r="T79" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="80" spans="1:25" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>411</v>
       </c>
       <c r="B80" t="s">
+        <v>27</v>
+      </c>
+      <c r="C80" t="s">
         <v>28</v>
       </c>
-      <c r="C80" t="s">
-        <v>29</v>
-      </c>
       <c r="D80" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F80">
         <v>207</v>
@@ -5910,19 +6111,19 @@
         <v>114</v>
       </c>
       <c r="I80" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J80" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L80" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M80" s="2">
         <v>43724</v>
       </c>
       <c r="N80" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O80">
         <v>-21.742880490000001</v>
@@ -5940,45 +6141,45 @@
         <v>3.2402029360000002</v>
       </c>
       <c r="T80" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>897</v>
       </c>
       <c r="B81" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C81" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D81" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F81">
         <v>162</v>
       </c>
       <c r="G81" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H81">
         <v>66</v>
       </c>
       <c r="J81" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L81" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M81" s="2">
         <v>43606</v>
       </c>
       <c r="N81" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="O81">
         <v>-22.419570199999999</v>
@@ -5996,45 +6197,45 @@
         <v>3.291518736</v>
       </c>
       <c r="T81" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="82" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>898</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C82" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D82" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E82" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F82">
         <v>173</v>
       </c>
       <c r="G82" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H82">
         <v>59</v>
       </c>
       <c r="J82" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L82" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M82" s="2">
         <v>43606</v>
       </c>
       <c r="N82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O82">
         <v>-20.783369960000002</v>
@@ -6052,45 +6253,45 @@
         <v>3.0650414220000002</v>
       </c>
       <c r="T82" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="83" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>899</v>
       </c>
       <c r="B83" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C83" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D83" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E83" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F83">
         <v>170</v>
       </c>
       <c r="G83" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H83">
         <v>54</v>
       </c>
       <c r="J83" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L83" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M83" s="2">
         <v>43606</v>
       </c>
       <c r="N83" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O83">
         <v>-21.849033429999999</v>
@@ -6108,45 +6309,45 @@
         <v>3.2954786569999999</v>
       </c>
       <c r="T83" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>900</v>
       </c>
       <c r="B84" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C84" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E84" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F84">
         <v>186</v>
       </c>
       <c r="G84" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H84">
         <v>79</v>
       </c>
       <c r="J84" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="L84" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M84" s="2">
         <v>43606</v>
       </c>
       <c r="N84" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O84">
         <v>-22.431477050000002</v>
@@ -6164,24 +6365,24 @@
         <v>3.219913746</v>
       </c>
       <c r="T84" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="85" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>412</v>
       </c>
       <c r="B85" t="s">
+        <v>27</v>
+      </c>
+      <c r="C85" t="s">
         <v>28</v>
       </c>
-      <c r="C85" t="s">
-        <v>29</v>
-      </c>
       <c r="D85" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E85" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F85">
         <v>143</v>
@@ -6193,16 +6394,16 @@
         <v>30</v>
       </c>
       <c r="J85" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L85" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M85" s="2">
         <v>43724</v>
       </c>
       <c r="N85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O85">
         <v>-21.54884002</v>
@@ -6220,24 +6421,24 @@
         <v>3.28186898</v>
       </c>
       <c r="T85" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="86" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>413</v>
       </c>
       <c r="B86" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" t="s">
         <v>28</v>
       </c>
-      <c r="C86" t="s">
-        <v>29</v>
-      </c>
       <c r="D86" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E86" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F86">
         <v>137</v>
@@ -6249,16 +6450,16 @@
         <v>27</v>
       </c>
       <c r="J86" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L86" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M86" s="2">
         <v>43724</v>
       </c>
       <c r="N86" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O86">
         <v>-21.638472929999999</v>
@@ -6276,24 +6477,24 @@
         <v>3.201279199</v>
       </c>
       <c r="T86" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>414</v>
       </c>
       <c r="B87" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" t="s">
         <v>28</v>
       </c>
-      <c r="C87" t="s">
-        <v>29</v>
-      </c>
       <c r="D87" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E87" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F87">
         <v>149</v>
@@ -6305,16 +6506,16 @@
         <v>41</v>
       </c>
       <c r="J87" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L87" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M87" s="2">
         <v>43724</v>
       </c>
       <c r="N87" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O87">
         <v>-22.799760769999999</v>
@@ -6332,7 +6533,7 @@
         <v>3.2657776520000001</v>
       </c>
       <c r="T87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
